--- a/data/Specimen_maps/Field_map.xlsx
+++ b/data/Specimen_maps/Field_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/Specimen_maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911E46CB-FF2E-8947-B30A-37B575DE3E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE03AA39-AF7E-0B47-8E75-5F28A7781081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="3000" windowWidth="26040" windowHeight="13840" xr2:uid="{B41C46FB-D0F9-F940-9BF1-4B7C82FF3330}"/>
+    <workbookView xWindow="2380" yWindow="2960" windowWidth="26040" windowHeight="13840" xr2:uid="{B41C46FB-D0F9-F940-9BF1-4B7C82FF3330}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="30">
   <si>
     <t>Sr. No</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Field (Indonesia_1.0)</t>
+  </si>
+  <si>
+    <t>Field (South Africa)</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC969DC-FAC9-D041-8228-F7F5DC3C57CD}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -940,6 +943,35 @@
         <v>22</v>
       </c>
     </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>-34</v>
+      </c>
+      <c r="H17">
+        <v>23.35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Specimen_maps/Field_map.xlsx
+++ b/data/Specimen_maps/Field_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/Specimen_maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE03AA39-AF7E-0B47-8E75-5F28A7781081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938151D4-7BF6-3148-8E74-156FF584B5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="2960" windowWidth="26040" windowHeight="13840" xr2:uid="{B41C46FB-D0F9-F940-9BF1-4B7C82FF3330}"/>
+    <workbookView xWindow="2380" yWindow="2940" windowWidth="26040" windowHeight="13840" xr2:uid="{B41C46FB-D0F9-F940-9BF1-4B7C82FF3330}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
